--- a/data/trans_orig/IP74A1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP74A1_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto la hipoteca en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de la hipoteca en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>16388</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
